--- a/activityAnalysis/US_SPD_Sectionals.xlsx
+++ b/activityAnalysis/US_SPD_Sectionals.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rachaelnaphtal/Documents/JudgingAnalysis/activityAnalysis/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C731E2E2-7656-4142-8849-317A2F8728CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B908EB63-BD0A-1F44-AC4B-DAF083C2BE50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="12080" yWindow="2260" windowWidth="16640" windowHeight="15640" xr2:uid="{A676BBDF-E368-1745-B425-783D057168F8}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2374" uniqueCount="566">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2612" uniqueCount="570">
   <si>
     <t>2025 Eastern Sectional and Pairs Final</t>
   </si>
@@ -1736,12 +1736,24 @@
   <si>
     <t>Katherine Imperatore</t>
   </si>
+  <si>
+    <t>Wendy Mlinar</t>
+  </si>
+  <si>
+    <t>Jennifer Marker Johnson</t>
+  </si>
+  <si>
+    <t>Krissa Price</t>
+  </si>
+  <si>
+    <t>Whitney Gaynor</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="14">
+  <fonts count="15">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1827,6 +1839,12 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Helvetica Neue"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -1848,7 +1866,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1863,6 +1881,7 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3736,6 +3755,24 @@
       <c r="CB8" t="s">
         <v>159</v>
       </c>
+      <c r="CD8" t="s">
+        <v>23</v>
+      </c>
+      <c r="CE8" t="s">
+        <v>33</v>
+      </c>
+      <c r="CG8" t="s">
+        <v>429</v>
+      </c>
+      <c r="CH8" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="CJ8" s="14" t="s">
+        <v>110</v>
+      </c>
+      <c r="CK8" s="14" t="s">
+        <v>541</v>
+      </c>
     </row>
     <row r="9" spans="1:89" ht="17">
       <c r="A9" s="7" t="s">
@@ -3917,6 +3954,24 @@
       <c r="CB9" t="s">
         <v>33</v>
       </c>
+      <c r="CD9" t="s">
+        <v>224</v>
+      </c>
+      <c r="CE9" t="s">
+        <v>541</v>
+      </c>
+      <c r="CG9" t="s">
+        <v>361</v>
+      </c>
+      <c r="CH9" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="CJ9" s="14" t="s">
+        <v>260</v>
+      </c>
+      <c r="CK9" s="14" t="s">
+        <v>541</v>
+      </c>
     </row>
     <row r="10" spans="1:89" ht="17">
       <c r="A10" s="1"/>
@@ -4089,6 +4144,24 @@
       </c>
       <c r="CB10" t="s">
         <v>540</v>
+      </c>
+      <c r="CD10" t="s">
+        <v>85</v>
+      </c>
+      <c r="CE10" t="s">
+        <v>465</v>
+      </c>
+      <c r="CG10" t="s">
+        <v>65</v>
+      </c>
+      <c r="CH10" s="14" t="s">
+        <v>540</v>
+      </c>
+      <c r="CJ10" s="14" t="s">
+        <v>262</v>
+      </c>
+      <c r="CK10" s="14" t="s">
+        <v>465</v>
       </c>
     </row>
     <row r="11" spans="1:89" ht="17">
@@ -4259,6 +4332,24 @@
       <c r="CB11" t="s">
         <v>541</v>
       </c>
+      <c r="CD11" t="s">
+        <v>150</v>
+      </c>
+      <c r="CE11" t="s">
+        <v>41</v>
+      </c>
+      <c r="CG11" t="s">
+        <v>362</v>
+      </c>
+      <c r="CH11" s="14" t="s">
+        <v>465</v>
+      </c>
+      <c r="CJ11" s="14" t="s">
+        <v>262</v>
+      </c>
+      <c r="CK11" s="14" t="s">
+        <v>541</v>
+      </c>
     </row>
     <row r="12" spans="1:89" ht="17">
       <c r="A12" s="7" t="s">
@@ -4435,6 +4526,24 @@
       </c>
       <c r="CB12" t="s">
         <v>57</v>
+      </c>
+      <c r="CD12" t="s">
+        <v>346</v>
+      </c>
+      <c r="CE12" t="s">
+        <v>541</v>
+      </c>
+      <c r="CG12" t="s">
+        <v>362</v>
+      </c>
+      <c r="CH12" s="14" t="s">
+        <v>541</v>
+      </c>
+      <c r="CJ12" s="14" t="s">
+        <v>213</v>
+      </c>
+      <c r="CK12" s="14" t="s">
+        <v>541</v>
       </c>
     </row>
     <row r="13" spans="1:89" ht="17">
@@ -4613,6 +4722,24 @@
       <c r="CB13" t="s">
         <v>41</v>
       </c>
+      <c r="CD13" t="s">
+        <v>21</v>
+      </c>
+      <c r="CE13" t="s">
+        <v>541</v>
+      </c>
+      <c r="CG13" t="s">
+        <v>199</v>
+      </c>
+      <c r="CH13" s="14" t="s">
+        <v>541</v>
+      </c>
+      <c r="CJ13" s="14" t="s">
+        <v>149</v>
+      </c>
+      <c r="CK13" s="14" t="s">
+        <v>41</v>
+      </c>
     </row>
     <row r="14" spans="1:89" ht="17">
       <c r="A14" s="1"/>
@@ -4794,6 +4921,24 @@
       <c r="CB14" t="s">
         <v>541</v>
       </c>
+      <c r="CD14" t="s">
+        <v>254</v>
+      </c>
+      <c r="CE14" t="s">
+        <v>39</v>
+      </c>
+      <c r="CG14" t="s">
+        <v>313</v>
+      </c>
+      <c r="CH14" s="14" t="s">
+        <v>541</v>
+      </c>
+      <c r="CJ14" s="14" t="s">
+        <v>149</v>
+      </c>
+      <c r="CK14" s="14" t="s">
+        <v>465</v>
+      </c>
     </row>
     <row r="15" spans="1:89" ht="17">
       <c r="A15" s="7" t="s">
@@ -4971,6 +5116,24 @@
       <c r="CB15" t="s">
         <v>259</v>
       </c>
+      <c r="CD15" t="s">
+        <v>109</v>
+      </c>
+      <c r="CE15" t="s">
+        <v>39</v>
+      </c>
+      <c r="CG15" t="s">
+        <v>483</v>
+      </c>
+      <c r="CH15" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="CJ15" s="14" t="s">
+        <v>149</v>
+      </c>
+      <c r="CK15" s="14" t="s">
+        <v>159</v>
+      </c>
     </row>
     <row r="16" spans="1:89" ht="17">
       <c r="A16" s="7" t="s">
@@ -5148,8 +5311,26 @@
       <c r="CB16" t="s">
         <v>465</v>
       </c>
-    </row>
-    <row r="17" spans="1:80" ht="17">
+      <c r="CD16" t="s">
+        <v>109</v>
+      </c>
+      <c r="CE16" t="s">
+        <v>57</v>
+      </c>
+      <c r="CG16" t="s">
+        <v>222</v>
+      </c>
+      <c r="CH16" s="14" t="s">
+        <v>39</v>
+      </c>
+      <c r="CJ16" s="14" t="s">
+        <v>149</v>
+      </c>
+      <c r="CK16" s="14" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="17" spans="1:89" ht="17">
       <c r="A17" s="7" t="s">
         <v>164</v>
       </c>
@@ -5329,8 +5510,26 @@
       <c r="CB17" t="s">
         <v>541</v>
       </c>
-    </row>
-    <row r="18" spans="1:80" ht="17">
+      <c r="CD17" t="s">
+        <v>109</v>
+      </c>
+      <c r="CE17" t="s">
+        <v>83</v>
+      </c>
+      <c r="CG17" t="s">
+        <v>80</v>
+      </c>
+      <c r="CH17" s="14" t="s">
+        <v>542</v>
+      </c>
+      <c r="CJ17" s="14" t="s">
+        <v>149</v>
+      </c>
+      <c r="CK17" s="14" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="18" spans="1:89" ht="17">
       <c r="A18" s="7" t="s">
         <v>361</v>
       </c>
@@ -5510,8 +5709,26 @@
       <c r="CB18" t="s">
         <v>541</v>
       </c>
-    </row>
-    <row r="19" spans="1:80" ht="17">
+      <c r="CD18" t="s">
+        <v>109</v>
+      </c>
+      <c r="CE18" t="s">
+        <v>33</v>
+      </c>
+      <c r="CG18" t="s">
+        <v>80</v>
+      </c>
+      <c r="CH18" s="14" t="s">
+        <v>540</v>
+      </c>
+      <c r="CJ18" s="14" t="s">
+        <v>469</v>
+      </c>
+      <c r="CK18" s="14" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="19" spans="1:89" ht="17">
       <c r="A19" s="7" t="s">
         <v>242</v>
       </c>
@@ -5687,8 +5904,26 @@
       <c r="CB19" t="s">
         <v>465</v>
       </c>
-    </row>
-    <row r="20" spans="1:80" ht="17">
+      <c r="CD19" t="s">
+        <v>167</v>
+      </c>
+      <c r="CE19" t="s">
+        <v>541</v>
+      </c>
+      <c r="CG19" t="s">
+        <v>333</v>
+      </c>
+      <c r="CH19" s="14" t="s">
+        <v>541</v>
+      </c>
+      <c r="CJ19" s="14" t="s">
+        <v>178</v>
+      </c>
+      <c r="CK19" s="14" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="20" spans="1:89" ht="17">
       <c r="A20" s="7" t="s">
         <v>234</v>
       </c>
@@ -5868,8 +6103,26 @@
       <c r="CB20" t="s">
         <v>541</v>
       </c>
-    </row>
-    <row r="21" spans="1:80" ht="17">
+      <c r="CD20" t="s">
+        <v>49</v>
+      </c>
+      <c r="CE20" t="s">
+        <v>541</v>
+      </c>
+      <c r="CG20" t="s">
+        <v>131</v>
+      </c>
+      <c r="CH20" s="14" t="s">
+        <v>465</v>
+      </c>
+      <c r="CJ20" s="14" t="s">
+        <v>306</v>
+      </c>
+      <c r="CK20" s="14" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="21" spans="1:89" ht="17">
       <c r="A21" s="7" t="s">
         <v>424</v>
       </c>
@@ -6053,8 +6306,26 @@
       <c r="CB21" t="s">
         <v>541</v>
       </c>
-    </row>
-    <row r="22" spans="1:80" ht="17">
+      <c r="CD21" t="s">
+        <v>49</v>
+      </c>
+      <c r="CE21" t="s">
+        <v>540</v>
+      </c>
+      <c r="CG21" t="s">
+        <v>131</v>
+      </c>
+      <c r="CH21" s="14" t="s">
+        <v>541</v>
+      </c>
+      <c r="CJ21" s="14" t="s">
+        <v>306</v>
+      </c>
+      <c r="CK21" s="14" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="22" spans="1:89" ht="17">
       <c r="A22" s="7" t="s">
         <v>204</v>
       </c>
@@ -6234,8 +6505,26 @@
       <c r="CB22" t="s">
         <v>542</v>
       </c>
-    </row>
-    <row r="23" spans="1:80" ht="17">
+      <c r="CD22" t="s">
+        <v>227</v>
+      </c>
+      <c r="CE22" t="s">
+        <v>465</v>
+      </c>
+      <c r="CG22" t="s">
+        <v>193</v>
+      </c>
+      <c r="CH22" s="14" t="s">
+        <v>83</v>
+      </c>
+      <c r="CJ22" s="14" t="s">
+        <v>144</v>
+      </c>
+      <c r="CK22" s="14" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="23" spans="1:89" ht="17">
       <c r="A23" s="7" t="s">
         <v>292</v>
       </c>
@@ -6411,8 +6700,26 @@
       <c r="CB23" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="24" spans="1:80" ht="17">
+      <c r="CD23" t="s">
+        <v>86</v>
+      </c>
+      <c r="CE23" t="s">
+        <v>541</v>
+      </c>
+      <c r="CG23" t="s">
+        <v>232</v>
+      </c>
+      <c r="CH23" s="14" t="s">
+        <v>159</v>
+      </c>
+      <c r="CJ23" s="14" t="s">
+        <v>69</v>
+      </c>
+      <c r="CK23" s="14" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="24" spans="1:89" ht="17">
       <c r="A24" s="1" t="s">
         <v>235</v>
       </c>
@@ -6588,8 +6895,26 @@
       <c r="CB24" t="s">
         <v>541</v>
       </c>
-    </row>
-    <row r="25" spans="1:80" ht="17">
+      <c r="CD24" t="s">
+        <v>64</v>
+      </c>
+      <c r="CE24" t="s">
+        <v>465</v>
+      </c>
+      <c r="CG24" t="s">
+        <v>567</v>
+      </c>
+      <c r="CH24" s="14" t="s">
+        <v>541</v>
+      </c>
+      <c r="CJ24" s="14" t="s">
+        <v>142</v>
+      </c>
+      <c r="CK24" s="14" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="25" spans="1:89" ht="17">
       <c r="A25" s="7" t="s">
         <v>260</v>
       </c>
@@ -6765,8 +7090,26 @@
       <c r="CB25" t="s">
         <v>541</v>
       </c>
-    </row>
-    <row r="26" spans="1:80" ht="17">
+      <c r="CD25" t="s">
+        <v>253</v>
+      </c>
+      <c r="CE25" t="s">
+        <v>39</v>
+      </c>
+      <c r="CG25" t="s">
+        <v>98</v>
+      </c>
+      <c r="CH25" s="14" t="s">
+        <v>541</v>
+      </c>
+      <c r="CJ25" s="14" t="s">
+        <v>156</v>
+      </c>
+      <c r="CK25" s="14" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="26" spans="1:89" ht="17">
       <c r="A26" s="1"/>
       <c r="B26" s="1"/>
       <c r="C26" s="1"/>
@@ -6946,8 +7289,26 @@
       <c r="CB26" t="s">
         <v>259</v>
       </c>
-    </row>
-    <row r="27" spans="1:80" ht="17">
+      <c r="CD26" t="s">
+        <v>253</v>
+      </c>
+      <c r="CE26" t="s">
+        <v>57</v>
+      </c>
+      <c r="CG26" t="s">
+        <v>38</v>
+      </c>
+      <c r="CH26" s="14" t="s">
+        <v>39</v>
+      </c>
+      <c r="CJ26" s="14" t="s">
+        <v>168</v>
+      </c>
+      <c r="CK26" s="14" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="27" spans="1:89" ht="17">
       <c r="A27" s="7" t="s">
         <v>23</v>
       </c>
@@ -7131,8 +7492,26 @@
       <c r="CB27" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="28" spans="1:80" ht="17">
+      <c r="CD27" t="s">
+        <v>89</v>
+      </c>
+      <c r="CE27" t="s">
+        <v>541</v>
+      </c>
+      <c r="CG27" t="s">
+        <v>410</v>
+      </c>
+      <c r="CH27" s="14" t="s">
+        <v>465</v>
+      </c>
+      <c r="CJ27" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="CK27" s="14" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="28" spans="1:89" ht="17">
       <c r="A28" s="7" t="s">
         <v>17</v>
       </c>
@@ -7316,8 +7695,26 @@
       <c r="CB28" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="29" spans="1:80" ht="17">
+      <c r="CD28" t="s">
+        <v>59</v>
+      </c>
+      <c r="CE28" t="s">
+        <v>542</v>
+      </c>
+      <c r="CG28" t="s">
+        <v>410</v>
+      </c>
+      <c r="CH28" s="14" t="s">
+        <v>541</v>
+      </c>
+      <c r="CJ28" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="CK28" s="14" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="29" spans="1:89" ht="17">
       <c r="A29" s="7" t="s">
         <v>327</v>
       </c>
@@ -7501,8 +7898,26 @@
       <c r="CB29" t="s">
         <v>541</v>
       </c>
-    </row>
-    <row r="30" spans="1:80" ht="17">
+      <c r="CD29" t="s">
+        <v>256</v>
+      </c>
+      <c r="CE29" t="s">
+        <v>159</v>
+      </c>
+      <c r="CG29" t="s">
+        <v>51</v>
+      </c>
+      <c r="CH29" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="CJ29" s="14" t="s">
+        <v>158</v>
+      </c>
+      <c r="CK29" s="14" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="30" spans="1:89" ht="17">
       <c r="A30" s="7" t="s">
         <v>427</v>
       </c>
@@ -7686,8 +8101,26 @@
       <c r="CB30" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="31" spans="1:80" ht="17">
+      <c r="CD30" t="s">
+        <v>246</v>
+      </c>
+      <c r="CE30" t="s">
+        <v>41</v>
+      </c>
+      <c r="CG30" t="s">
+        <v>162</v>
+      </c>
+      <c r="CH30" s="14" t="s">
+        <v>541</v>
+      </c>
+      <c r="CJ30" s="14" t="s">
+        <v>158</v>
+      </c>
+      <c r="CK30" s="14" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="31" spans="1:89" ht="17">
       <c r="A31" s="7" t="s">
         <v>408</v>
       </c>
@@ -7871,8 +8304,26 @@
       <c r="CB31" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="32" spans="1:80" ht="17">
+      <c r="CD31" t="s">
+        <v>189</v>
+      </c>
+      <c r="CE31" t="s">
+        <v>541</v>
+      </c>
+      <c r="CG31" t="s">
+        <v>162</v>
+      </c>
+      <c r="CH31" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="CJ31" s="14" t="s">
+        <v>312</v>
+      </c>
+      <c r="CK31" s="14" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="32" spans="1:89" ht="17">
       <c r="A32" s="7" t="s">
         <v>86</v>
       </c>
@@ -8040,8 +8491,26 @@
       <c r="CB32" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="33" spans="1:80" ht="17">
+      <c r="CD32" t="s">
+        <v>422</v>
+      </c>
+      <c r="CE32" t="s">
+        <v>39</v>
+      </c>
+      <c r="CG32" t="s">
+        <v>568</v>
+      </c>
+      <c r="CH32" s="14" t="s">
+        <v>465</v>
+      </c>
+      <c r="CJ32" s="14" t="s">
+        <v>462</v>
+      </c>
+      <c r="CK32" s="14" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="33" spans="1:89" ht="17">
       <c r="A33" s="8" t="s">
         <v>442</v>
       </c>
@@ -8205,8 +8674,26 @@
       <c r="CB33" t="s">
         <v>542</v>
       </c>
-    </row>
-    <row r="34" spans="1:80" ht="17">
+      <c r="CD33" t="s">
+        <v>515</v>
+      </c>
+      <c r="CE33" t="s">
+        <v>541</v>
+      </c>
+      <c r="CG33" t="s">
+        <v>568</v>
+      </c>
+      <c r="CH33" s="14" t="s">
+        <v>541</v>
+      </c>
+      <c r="CJ33" s="14" t="s">
+        <v>521</v>
+      </c>
+      <c r="CK33" s="14" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="34" spans="1:89" ht="17">
       <c r="A34" s="7" t="s">
         <v>271</v>
       </c>
@@ -8378,8 +8865,26 @@
       <c r="CB34" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="35" spans="1:80" ht="17">
+      <c r="CD34" t="s">
+        <v>515</v>
+      </c>
+      <c r="CE34" t="s">
+        <v>465</v>
+      </c>
+      <c r="CG34" t="s">
+        <v>335</v>
+      </c>
+      <c r="CH34" s="14" t="s">
+        <v>39</v>
+      </c>
+      <c r="CJ34" s="14" t="s">
+        <v>302</v>
+      </c>
+      <c r="CK34" s="14" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="35" spans="1:89" ht="17">
       <c r="A35" s="1"/>
       <c r="B35" s="1"/>
       <c r="C35" s="1"/>
@@ -8551,8 +9056,26 @@
       <c r="CB35" t="s">
         <v>465</v>
       </c>
-    </row>
-    <row r="36" spans="1:80" ht="17">
+      <c r="CD35" t="s">
+        <v>423</v>
+      </c>
+      <c r="CE35" t="s">
+        <v>39</v>
+      </c>
+      <c r="CG35" t="s">
+        <v>212</v>
+      </c>
+      <c r="CH35" s="14" t="s">
+        <v>39</v>
+      </c>
+      <c r="CJ35" s="14" t="s">
+        <v>307</v>
+      </c>
+      <c r="CK35" s="14" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="36" spans="1:89" ht="17">
       <c r="A36" s="1"/>
       <c r="B36" s="1"/>
       <c r="C36" s="1"/>
@@ -8708,8 +9231,26 @@
       <c r="CB36" t="s">
         <v>465</v>
       </c>
-    </row>
-    <row r="37" spans="1:80" ht="17">
+      <c r="CD36" t="s">
+        <v>423</v>
+      </c>
+      <c r="CE36" t="s">
+        <v>57</v>
+      </c>
+      <c r="CG36" t="s">
+        <v>301</v>
+      </c>
+      <c r="CH36" s="14" t="s">
+        <v>541</v>
+      </c>
+      <c r="CJ36" s="14" t="s">
+        <v>307</v>
+      </c>
+      <c r="CK36" s="14" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="37" spans="1:89" ht="17">
       <c r="A37" s="7" t="s">
         <v>67</v>
       </c>
@@ -8881,8 +9422,26 @@
       <c r="CB37" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="38" spans="1:80" ht="20">
+      <c r="CD37" t="s">
+        <v>292</v>
+      </c>
+      <c r="CE37" t="s">
+        <v>541</v>
+      </c>
+      <c r="CG37" t="s">
+        <v>341</v>
+      </c>
+      <c r="CH37" s="14" t="s">
+        <v>465</v>
+      </c>
+      <c r="CJ37" s="14" t="s">
+        <v>305</v>
+      </c>
+      <c r="CK37" s="14" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="38" spans="1:89" ht="20">
       <c r="A38" s="1"/>
       <c r="B38" s="1"/>
       <c r="C38" s="1"/>
@@ -9046,8 +9605,26 @@
       <c r="CB38" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="39" spans="1:80" ht="17">
+      <c r="CD38" t="s">
+        <v>334</v>
+      </c>
+      <c r="CE38" t="s">
+        <v>465</v>
+      </c>
+      <c r="CG38" t="s">
+        <v>341</v>
+      </c>
+      <c r="CH38" s="14" t="s">
+        <v>541</v>
+      </c>
+      <c r="CJ38" s="14" t="s">
+        <v>470</v>
+      </c>
+      <c r="CK38" s="14" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="39" spans="1:89" ht="17">
       <c r="A39" s="1"/>
       <c r="B39" s="1"/>
       <c r="C39" s="1"/>
@@ -9211,8 +9788,26 @@
       <c r="CB39" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="40" spans="1:80" ht="17">
+      <c r="CD39" t="s">
+        <v>77</v>
+      </c>
+      <c r="CE39" t="s">
+        <v>465</v>
+      </c>
+      <c r="CG39" t="s">
+        <v>295</v>
+      </c>
+      <c r="CH39" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="CJ39" s="14" t="s">
+        <v>140</v>
+      </c>
+      <c r="CK39" s="14" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="40" spans="1:89" ht="17">
       <c r="A40" s="1"/>
       <c r="B40" s="1"/>
       <c r="C40" s="1"/>
@@ -9359,8 +9954,26 @@
       <c r="CB40" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="41" spans="1:80" ht="17">
+      <c r="CD40" t="s">
+        <v>77</v>
+      </c>
+      <c r="CE40" t="s">
+        <v>541</v>
+      </c>
+      <c r="CG40" t="s">
+        <v>141</v>
+      </c>
+      <c r="CH40" s="14" t="s">
+        <v>465</v>
+      </c>
+      <c r="CJ40" s="14" t="s">
+        <v>354</v>
+      </c>
+      <c r="CK40" s="14" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="41" spans="1:89" ht="17">
       <c r="A41" s="1"/>
       <c r="B41" s="1"/>
       <c r="C41" s="1"/>
@@ -9516,8 +10129,26 @@
       <c r="CB41" t="s">
         <v>266</v>
       </c>
-    </row>
-    <row r="42" spans="1:80" ht="17">
+      <c r="CD41" t="s">
+        <v>510</v>
+      </c>
+      <c r="CE41" t="s">
+        <v>541</v>
+      </c>
+      <c r="CG41" t="s">
+        <v>228</v>
+      </c>
+      <c r="CH41" s="14" t="s">
+        <v>540</v>
+      </c>
+      <c r="CJ41" s="14" t="s">
+        <v>354</v>
+      </c>
+      <c r="CK41" s="14" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="42" spans="1:89" ht="17">
       <c r="A42" s="1"/>
       <c r="B42" s="1"/>
       <c r="C42" s="1"/>
@@ -9663,8 +10294,26 @@
       <c r="CB42" t="s">
         <v>266</v>
       </c>
-    </row>
-    <row r="43" spans="1:80" ht="17">
+      <c r="CD42" t="s">
+        <v>510</v>
+      </c>
+      <c r="CE42" t="s">
+        <v>540</v>
+      </c>
+      <c r="CG42" t="s">
+        <v>268</v>
+      </c>
+      <c r="CH42" s="14" t="s">
+        <v>541</v>
+      </c>
+      <c r="CJ42" s="14" t="s">
+        <v>151</v>
+      </c>
+      <c r="CK42" s="14" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="43" spans="1:89" ht="17">
       <c r="A43" s="1"/>
       <c r="B43" s="1"/>
       <c r="C43" s="1"/>
@@ -9796,8 +10445,26 @@
       <c r="CB43" t="s">
         <v>550</v>
       </c>
-    </row>
-    <row r="44" spans="1:80" ht="20">
+      <c r="CD43" t="s">
+        <v>108</v>
+      </c>
+      <c r="CE43" t="s">
+        <v>33</v>
+      </c>
+      <c r="CG43" t="s">
+        <v>268</v>
+      </c>
+      <c r="CH43" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="CJ43" s="14" t="s">
+        <v>511</v>
+      </c>
+      <c r="CK43" s="14" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="44" spans="1:89" ht="20">
       <c r="A44" s="1"/>
       <c r="B44" s="1"/>
       <c r="C44" s="1"/>
@@ -9921,8 +10588,26 @@
       <c r="CB44" t="s">
         <v>393</v>
       </c>
-    </row>
-    <row r="45" spans="1:80" ht="20">
+      <c r="CD44" t="s">
+        <v>108</v>
+      </c>
+      <c r="CE44" t="s">
+        <v>83</v>
+      </c>
+      <c r="CG44" t="s">
+        <v>28</v>
+      </c>
+      <c r="CH44" s="14" t="s">
+        <v>541</v>
+      </c>
+      <c r="CJ44" s="14" t="s">
+        <v>495</v>
+      </c>
+      <c r="CK44" s="14" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="45" spans="1:89" ht="20">
       <c r="A45" s="1"/>
       <c r="B45" s="1"/>
       <c r="C45" s="1"/>
@@ -10036,8 +10721,26 @@
       <c r="BY45" t="s">
         <v>266</v>
       </c>
-    </row>
-    <row r="46" spans="1:80" ht="17">
+      <c r="CD45" t="s">
+        <v>566</v>
+      </c>
+      <c r="CE45" t="s">
+        <v>465</v>
+      </c>
+      <c r="CG45" t="s">
+        <v>329</v>
+      </c>
+      <c r="CH45" s="14" t="s">
+        <v>465</v>
+      </c>
+      <c r="CJ45" s="14" t="s">
+        <v>495</v>
+      </c>
+      <c r="CK45" s="14" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="46" spans="1:89" ht="17">
       <c r="A46" s="1"/>
       <c r="B46" s="1"/>
       <c r="C46" s="1"/>
@@ -10151,8 +10854,20 @@
       <c r="BY46" t="s">
         <v>266</v>
       </c>
-    </row>
-    <row r="47" spans="1:80" ht="17">
+      <c r="CG46" t="s">
+        <v>329</v>
+      </c>
+      <c r="CH46" s="14" t="s">
+        <v>541</v>
+      </c>
+      <c r="CJ46" s="14" t="s">
+        <v>569</v>
+      </c>
+      <c r="CK46" s="14" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="47" spans="1:89" ht="17">
       <c r="A47" s="1"/>
       <c r="B47" s="1"/>
       <c r="C47" s="1"/>
@@ -10252,8 +10967,20 @@
       <c r="BY47" t="s">
         <v>550</v>
       </c>
-    </row>
-    <row r="48" spans="1:80" ht="17">
+      <c r="CG47" t="s">
+        <v>340</v>
+      </c>
+      <c r="CH47" s="14" t="s">
+        <v>541</v>
+      </c>
+      <c r="CJ47" s="14" t="s">
+        <v>569</v>
+      </c>
+      <c r="CK47" s="14" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="48" spans="1:89" ht="17">
       <c r="A48" s="1"/>
       <c r="B48" s="1"/>
       <c r="C48" s="1"/>
@@ -10356,6 +11083,12 @@
       </c>
       <c r="BY48" t="s">
         <v>393</v>
+      </c>
+      <c r="CJ48" s="14" t="s">
+        <v>215</v>
+      </c>
+      <c r="CK48" s="14" t="s">
+        <v>541</v>
       </c>
     </row>
     <row r="49" spans="1:74">

--- a/activityAnalysis/US_SPD_Sectionals.xlsx
+++ b/activityAnalysis/US_SPD_Sectionals.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rachaelnaphtal/Documents/JudgingAnalysis/activityAnalysis/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B908EB63-BD0A-1F44-AC4B-DAF083C2BE50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1FE2746-2E9E-FD4F-ACA3-AE4CE8FE1973}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="12080" yWindow="2260" windowWidth="16640" windowHeight="15640" xr2:uid="{A676BBDF-E368-1745-B425-783D057168F8}"/>
   </bookViews>
@@ -1266,9 +1266,6 @@
     <t>Rachael Naphtal Einstein</t>
   </si>
   <si>
-    <t>Kitty DeLio LaForte</t>
-  </si>
-  <si>
     <t>Katherine Williamson</t>
   </si>
   <si>
@@ -1747,6 +1744,9 @@
   </si>
   <si>
     <t>Whitney Gaynor</t>
+  </si>
+  <si>
+    <t>Kitty DeLio-LaForte</t>
   </si>
 </sst>
 </file>
@@ -2230,17 +2230,17 @@
   <sheetData>
     <row r="1" spans="1:89">
       <c r="A1" s="1" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
       <c r="D1" s="1" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
       <c r="G1" s="1" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H1" s="1"/>
       <c r="I1" s="1"/>
@@ -2320,80 +2320,80 @@
       <c r="BA1" s="1"/>
       <c r="BB1" s="1"/>
       <c r="BC1" s="1" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="BD1" s="1"/>
       <c r="BE1" s="1"/>
       <c r="BF1" s="1" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="BG1" s="1"/>
       <c r="BH1" s="1"/>
       <c r="BI1" s="1" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="BJ1" s="1"/>
       <c r="BK1" s="1"/>
       <c r="BL1" s="1" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="BM1" s="1"/>
       <c r="BN1" s="1"/>
       <c r="BO1" s="1" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="BP1" s="1"/>
       <c r="BQ1" s="1"/>
       <c r="BR1" s="1" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="BS1" s="1"/>
       <c r="BU1" s="1" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="BV1" s="1"/>
       <c r="BW1" s="1"/>
       <c r="BX1" s="1" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="BY1" s="1"/>
       <c r="BZ1" s="1"/>
       <c r="CA1" s="1" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="CB1" s="1"/>
       <c r="CD1" s="1" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="CE1" s="1"/>
       <c r="CF1" s="1"/>
       <c r="CG1" s="1" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="CH1" s="1"/>
       <c r="CI1" s="1"/>
       <c r="CJ1" s="1" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="CK1" s="1"/>
     </row>
     <row r="2" spans="1:89">
       <c r="A2" s="2" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="2" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F2" s="1"/>
       <c r="G2" s="2" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H2" s="2" t="s">
         <v>16</v>
@@ -2503,82 +2503,82 @@
       </c>
       <c r="BB2" s="1"/>
       <c r="BC2" s="2" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="BD2" s="2" t="s">
         <v>16</v>
       </c>
       <c r="BE2" s="1"/>
       <c r="BF2" s="2" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="BG2" s="2" t="s">
         <v>16</v>
       </c>
       <c r="BH2" s="1"/>
       <c r="BI2" s="2" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="BJ2" s="2" t="s">
         <v>16</v>
       </c>
       <c r="BK2" s="1"/>
       <c r="BL2" s="2" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="BM2" s="2" t="s">
         <v>16</v>
       </c>
       <c r="BN2" s="1"/>
       <c r="BO2" s="2" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="BP2" s="2" t="s">
         <v>16</v>
       </c>
       <c r="BQ2" s="1"/>
       <c r="BR2" s="2" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="BS2" s="2" t="s">
         <v>16</v>
       </c>
       <c r="BU2" s="2" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="BV2" s="2" t="s">
         <v>16</v>
       </c>
       <c r="BW2" s="1"/>
       <c r="BX2" s="2" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="BY2" s="2" t="s">
         <v>16</v>
       </c>
       <c r="BZ2" s="1"/>
       <c r="CA2" s="2" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="CB2" s="2" t="s">
         <v>16</v>
       </c>
       <c r="CD2" s="2" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="CE2" s="2" t="s">
         <v>16</v>
       </c>
       <c r="CF2" s="1"/>
       <c r="CG2" s="2" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="CH2" s="2" t="s">
         <v>16</v>
       </c>
       <c r="CI2" s="1"/>
       <c r="CJ2" s="2" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="CK2" s="2" t="s">
         <v>16</v>
@@ -2603,7 +2603,7 @@
         <v>144</v>
       </c>
       <c r="H3" s="7" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="I3" s="1"/>
       <c r="J3" s="3" t="s">
@@ -2726,14 +2726,14 @@
       </c>
       <c r="BH3" s="1"/>
       <c r="BI3" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="BJ3" s="1" t="s">
         <v>39</v>
       </c>
       <c r="BK3" s="1"/>
       <c r="BL3" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="BM3" s="7" t="s">
         <v>37</v>
@@ -2754,19 +2754,19 @@
         <v>219</v>
       </c>
       <c r="BV3" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="BX3" t="s">
         <v>70</v>
       </c>
       <c r="BY3" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="CA3" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="CB3" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="CD3" t="s">
         <v>347</v>
@@ -2775,7 +2775,7 @@
         <v>61</v>
       </c>
       <c r="CG3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="CH3" t="s">
         <v>61</v>
@@ -2806,7 +2806,7 @@
         <v>244</v>
       </c>
       <c r="H4" s="7" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="I4" s="1"/>
       <c r="J4" s="1" t="s">
@@ -2953,7 +2953,7 @@
         <v>387</v>
       </c>
       <c r="BV4" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="BX4" t="s">
         <v>361</v>
@@ -2974,13 +2974,13 @@
         <v>266</v>
       </c>
       <c r="CG4" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="CH4" t="s">
         <v>266</v>
       </c>
       <c r="CJ4" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="CK4" t="s">
         <v>266</v>
@@ -2991,14 +2991,14 @@
         <v>120</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="C5" s="1"/>
       <c r="D5" s="7" t="s">
         <v>75</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="F5" s="1"/>
       <c r="G5" s="1"/>
@@ -3113,14 +3113,14 @@
       </c>
       <c r="BE5" s="1"/>
       <c r="BF5" s="7" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="BG5" s="7" t="s">
         <v>72</v>
       </c>
       <c r="BH5" s="1"/>
       <c r="BI5" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="BJ5" s="7" t="s">
         <v>37</v>
@@ -3133,7 +3133,7 @@
         <v>37</v>
       </c>
       <c r="BO5" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="BP5" s="7" t="s">
         <v>37</v>
@@ -3148,28 +3148,28 @@
         <v>52</v>
       </c>
       <c r="BV5" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="BX5" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="BY5" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="CA5" t="s">
         <v>290</v>
       </c>
       <c r="CB5" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="CD5" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="CE5" t="s">
         <v>266</v>
       </c>
       <c r="CG5" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="CH5" t="s">
         <v>266</v>
@@ -3186,14 +3186,14 @@
         <v>107</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="C6" s="1"/>
       <c r="D6" s="7" t="s">
         <v>60</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="F6" s="1"/>
       <c r="G6" s="7" t="s">
@@ -3326,7 +3326,7 @@
       </c>
       <c r="BK6" s="1"/>
       <c r="BL6" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="BM6" t="s">
         <v>39</v>
@@ -3353,31 +3353,31 @@
         <v>292</v>
       </c>
       <c r="BY6" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="CA6" t="s">
         <v>55</v>
       </c>
       <c r="CB6" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="CD6" t="s">
         <v>143</v>
       </c>
       <c r="CE6" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="CG6" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="CH6" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="CJ6" t="s">
         <v>81</v>
       </c>
       <c r="CK6" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
     </row>
     <row r="7" spans="1:89" ht="20">
@@ -3521,13 +3521,13 @@
       </c>
       <c r="BK7" s="1"/>
       <c r="BL7" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="BM7" t="s">
         <v>39</v>
       </c>
       <c r="BO7" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="BP7" t="s">
         <v>71</v>
@@ -3542,13 +3542,13 @@
         <v>67</v>
       </c>
       <c r="BV7" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="BX7" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="BY7" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="CA7" t="s">
         <v>359</v>
@@ -3580,7 +3580,7 @@
         <v>102</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="C8" s="1"/>
       <c r="D8" s="7" t="s">
@@ -3747,7 +3747,7 @@
         <v>141</v>
       </c>
       <c r="BY8" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="CA8" t="s">
         <v>232</v>
@@ -3762,7 +3762,7 @@
         <v>33</v>
       </c>
       <c r="CG8" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="CH8" s="14" t="s">
         <v>41</v>
@@ -3771,7 +3771,7 @@
         <v>110</v>
       </c>
       <c r="CK8" s="14" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
     </row>
     <row r="9" spans="1:89" ht="17">
@@ -3786,14 +3786,14 @@
         <v>91</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="F9" s="1"/>
       <c r="G9" s="7" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="H9" s="7" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="I9" s="1"/>
       <c r="J9" s="1" t="s">
@@ -3940,13 +3940,13 @@
         <v>23</v>
       </c>
       <c r="BV9" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="BX9" t="s">
         <v>65</v>
       </c>
       <c r="BY9" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="CA9" t="s">
         <v>84</v>
@@ -3958,7 +3958,7 @@
         <v>224</v>
       </c>
       <c r="CE9" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="CG9" t="s">
         <v>361</v>
@@ -3970,7 +3970,7 @@
         <v>260</v>
       </c>
       <c r="CK9" s="14" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
     </row>
     <row r="10" spans="1:89" ht="17">
@@ -4116,7 +4116,7 @@
         <v>33</v>
       </c>
       <c r="BO10" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="BP10" t="s">
         <v>41</v>
@@ -4128,7 +4128,7 @@
         <v>33</v>
       </c>
       <c r="BU10" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="BV10" t="s">
         <v>259</v>
@@ -4137,31 +4137,31 @@
         <v>407</v>
       </c>
       <c r="BY10" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="CA10" t="s">
         <v>404</v>
       </c>
       <c r="CB10" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="CD10" t="s">
         <v>85</v>
       </c>
       <c r="CE10" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="CG10" t="s">
         <v>65</v>
       </c>
       <c r="CH10" s="14" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="CJ10" s="14" t="s">
         <v>262</v>
       </c>
       <c r="CK10" s="14" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="11" spans="1:89" ht="17">
@@ -4276,7 +4276,7 @@
       </c>
       <c r="BB11" s="1"/>
       <c r="BC11" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="BD11" s="7" t="s">
         <v>41</v>
@@ -4290,7 +4290,7 @@
       </c>
       <c r="BH11" s="1"/>
       <c r="BI11" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="BJ11" s="7" t="s">
         <v>37</v>
@@ -4318,10 +4318,10 @@
         <v>82</v>
       </c>
       <c r="BV11" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="BX11" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="BY11" t="s">
         <v>41</v>
@@ -4330,7 +4330,7 @@
         <v>113</v>
       </c>
       <c r="CB11" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="CD11" t="s">
         <v>150</v>
@@ -4342,13 +4342,13 @@
         <v>362</v>
       </c>
       <c r="CH11" s="14" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="CJ11" s="14" t="s">
         <v>262</v>
       </c>
       <c r="CK11" s="14" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
     </row>
     <row r="12" spans="1:89" ht="17">
@@ -4363,10 +4363,10 @@
       <c r="E12" s="1"/>
       <c r="F12" s="1"/>
       <c r="G12" s="7" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="H12" s="7" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="I12" s="1"/>
       <c r="J12" s="1" t="s">
@@ -4504,7 +4504,7 @@
         <v>72</v>
       </c>
       <c r="BR12" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="BS12" s="7" t="s">
         <v>37</v>
@@ -4519,7 +4519,7 @@
         <v>19</v>
       </c>
       <c r="BY12" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="CA12" t="s">
         <v>140</v>
@@ -4531,19 +4531,19 @@
         <v>346</v>
       </c>
       <c r="CE12" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="CG12" t="s">
         <v>362</v>
       </c>
       <c r="CH12" s="14" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="CJ12" s="14" t="s">
         <v>213</v>
       </c>
       <c r="CK12" s="14" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
     </row>
     <row r="13" spans="1:89" ht="17">
@@ -4554,10 +4554,10 @@
       <c r="E13" s="1"/>
       <c r="F13" s="1"/>
       <c r="G13" s="7" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H13" s="7" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="I13" s="1"/>
       <c r="J13" s="1" t="s">
@@ -4714,7 +4714,7 @@
         <v>123</v>
       </c>
       <c r="BY13" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="CA13" t="s">
         <v>207</v>
@@ -4726,13 +4726,13 @@
         <v>21</v>
       </c>
       <c r="CE13" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="CG13" t="s">
         <v>199</v>
       </c>
       <c r="CH13" s="14" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="CJ13" s="14" t="s">
         <v>149</v>
@@ -4753,7 +4753,7 @@
       </c>
       <c r="F14" s="1"/>
       <c r="G14" s="7" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="H14" s="7" t="s">
         <v>92</v>
@@ -4872,14 +4872,14 @@
       </c>
       <c r="BE14" s="1"/>
       <c r="BF14" s="7" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="BG14" s="7" t="s">
         <v>37</v>
       </c>
       <c r="BH14" s="1"/>
       <c r="BI14" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="BJ14" s="7" t="s">
         <v>37</v>
@@ -4892,7 +4892,7 @@
         <v>39</v>
       </c>
       <c r="BO14" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="BP14" t="s">
         <v>57</v>
@@ -4910,7 +4910,7 @@
         <v>39</v>
       </c>
       <c r="BX14" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="BY14" t="s">
         <v>57</v>
@@ -4919,7 +4919,7 @@
         <v>156</v>
       </c>
       <c r="CB14" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="CD14" t="s">
         <v>254</v>
@@ -4931,13 +4931,13 @@
         <v>313</v>
       </c>
       <c r="CH14" s="14" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="CJ14" s="14" t="s">
         <v>149</v>
       </c>
       <c r="CK14" s="14" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="15" spans="1:89" ht="17">
@@ -4955,7 +4955,7 @@
         <v>81</v>
       </c>
       <c r="H15" s="7" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="I15" s="1"/>
       <c r="J15" s="1" t="s">
@@ -5067,7 +5067,7 @@
       </c>
       <c r="BE15" s="1"/>
       <c r="BF15" s="1" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="BG15" s="7" t="s">
         <v>39</v>
@@ -5102,13 +5102,13 @@
         <v>109</v>
       </c>
       <c r="BV15" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="BX15" t="s">
         <v>162</v>
       </c>
       <c r="BY15" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="CA15" t="s">
         <v>142</v>
@@ -5123,7 +5123,7 @@
         <v>39</v>
       </c>
       <c r="CG15" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="CH15" s="14" t="s">
         <v>57</v>
@@ -5140,14 +5140,14 @@
         <v>196</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C16" s="1"/>
       <c r="D16" s="7" t="s">
         <v>44</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="F16" s="1"/>
       <c r="G16" s="1"/>
@@ -5262,7 +5262,7 @@
       </c>
       <c r="BE16" s="1"/>
       <c r="BF16" s="7" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="BG16" s="7" t="s">
         <v>57</v>
@@ -5297,19 +5297,19 @@
         <v>17</v>
       </c>
       <c r="BV16" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="BX16" t="s">
         <v>320</v>
       </c>
       <c r="BY16" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="CA16" t="s">
         <v>168</v>
       </c>
       <c r="CB16" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="CD16" t="s">
         <v>109</v>
@@ -5342,14 +5342,14 @@
         <v>108</v>
       </c>
       <c r="E17" s="7" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="F17" s="1"/>
       <c r="G17" s="7" t="s">
         <v>135</v>
       </c>
       <c r="H17" s="7" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="I17" s="1"/>
       <c r="J17" s="1"/>
@@ -5496,19 +5496,19 @@
         <v>329</v>
       </c>
       <c r="BV17" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="BX17" t="s">
         <v>50</v>
       </c>
       <c r="BY17" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="CA17" t="s">
         <v>149</v>
       </c>
       <c r="CB17" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="CD17" t="s">
         <v>109</v>
@@ -5520,7 +5520,7 @@
         <v>80</v>
       </c>
       <c r="CH17" s="14" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="CJ17" s="14" t="s">
         <v>149</v>
@@ -5548,7 +5548,7 @@
         <v>126</v>
       </c>
       <c r="H18" s="7" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="I18" s="1"/>
       <c r="J18" s="1" t="s">
@@ -5653,7 +5653,7 @@
       </c>
       <c r="BB18" s="1"/>
       <c r="BC18" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="BD18" s="7" t="s">
         <v>39</v>
@@ -5680,7 +5680,7 @@
         <v>53</v>
       </c>
       <c r="BO18" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="BP18" s="7" t="s">
         <v>37</v>
@@ -5707,7 +5707,7 @@
         <v>44</v>
       </c>
       <c r="CB18" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="CD18" t="s">
         <v>109</v>
@@ -5719,10 +5719,10 @@
         <v>80</v>
       </c>
       <c r="CH18" s="14" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="CJ18" s="14" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="CK18" s="14" t="s">
         <v>41</v>
@@ -5737,7 +5737,7 @@
       </c>
       <c r="C19" s="1"/>
       <c r="D19" s="7" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="E19" s="7" t="s">
         <v>39</v>
@@ -5855,7 +5855,7 @@
       </c>
       <c r="BE19" s="1"/>
       <c r="BF19" s="7" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="BG19" s="7" t="s">
         <v>57</v>
@@ -5869,7 +5869,7 @@
       </c>
       <c r="BK19" s="1"/>
       <c r="BL19" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="BM19" s="1" t="s">
         <v>259</v>
@@ -5890,7 +5890,7 @@
         <v>350</v>
       </c>
       <c r="BV19" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="BX19" t="s">
         <v>51</v>
@@ -5902,19 +5902,19 @@
         <v>227</v>
       </c>
       <c r="CB19" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="CD19" t="s">
         <v>167</v>
       </c>
       <c r="CE19" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="CG19" t="s">
         <v>333</v>
       </c>
       <c r="CH19" s="14" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="CJ19" s="14" t="s">
         <v>178</v>
@@ -5932,10 +5932,10 @@
       </c>
       <c r="C20" s="1"/>
       <c r="D20" s="7" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="E20" s="7" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="F20" s="1"/>
       <c r="G20" s="7" t="s">
@@ -6086,10 +6086,10 @@
         <v>37</v>
       </c>
       <c r="BU20" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="BV20" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="BX20" t="s">
         <v>177</v>
@@ -6101,30 +6101,30 @@
         <v>166</v>
       </c>
       <c r="CB20" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="CD20" t="s">
         <v>49</v>
       </c>
       <c r="CE20" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="CG20" t="s">
         <v>131</v>
       </c>
       <c r="CH20" s="14" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="CJ20" s="14" t="s">
         <v>306</v>
       </c>
       <c r="CK20" s="14" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="21" spans="1:89" ht="17">
       <c r="A21" s="7" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B21" s="7" t="s">
         <v>31</v>
@@ -6134,7 +6134,7 @@
         <v>233</v>
       </c>
       <c r="E21" s="7" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="F21" s="1"/>
       <c r="G21" s="1" t="s">
@@ -6250,7 +6250,7 @@
       </c>
       <c r="BB21" s="1"/>
       <c r="BC21" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="BD21" s="7" t="s">
         <v>41</v>
@@ -6264,14 +6264,14 @@
       </c>
       <c r="BH21" s="1"/>
       <c r="BI21" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="BJ21" s="7" t="s">
         <v>37</v>
       </c>
       <c r="BK21" s="1"/>
       <c r="BL21" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="BM21" t="s">
         <v>39</v>
@@ -6289,13 +6289,13 @@
         <v>37</v>
       </c>
       <c r="BU21" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="BV21" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="BX21" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="BY21" t="s">
         <v>39</v>
@@ -6304,25 +6304,25 @@
         <v>21</v>
       </c>
       <c r="CB21" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="CD21" t="s">
         <v>49</v>
       </c>
       <c r="CE21" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="CG21" t="s">
         <v>131</v>
       </c>
       <c r="CH21" s="14" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="CJ21" s="14" t="s">
         <v>306</v>
       </c>
       <c r="CK21" s="14" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
     </row>
     <row r="22" spans="1:89" ht="17">
@@ -6330,14 +6330,14 @@
         <v>204</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="C22" s="1"/>
       <c r="D22" s="7" t="s">
         <v>226</v>
       </c>
       <c r="E22" s="7" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="F22" s="1"/>
       <c r="G22" s="7" t="s">
@@ -6400,7 +6400,7 @@
       </c>
       <c r="AG22" s="1"/>
       <c r="AH22" s="1" t="s">
-        <v>409</v>
+        <v>569</v>
       </c>
       <c r="AI22" s="1" t="s">
         <v>223</v>
@@ -6449,7 +6449,7 @@
       </c>
       <c r="BB22" s="1"/>
       <c r="BC22" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="BD22" s="10" t="s">
         <v>39</v>
@@ -6482,34 +6482,34 @@
         <v>159</v>
       </c>
       <c r="BR22" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="BS22" t="s">
         <v>39</v>
       </c>
       <c r="BU22" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="BV22" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="BX22" t="s">
         <v>187</v>
       </c>
       <c r="BY22" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="CA22" t="s">
         <v>239</v>
       </c>
       <c r="CB22" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="CD22" t="s">
         <v>227</v>
       </c>
       <c r="CE22" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="CG22" t="s">
         <v>193</v>
@@ -6686,16 +6686,16 @@
         <v>245</v>
       </c>
       <c r="BV23" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="BX23" t="s">
         <v>205</v>
       </c>
       <c r="BY23" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="CA23" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="CB23" t="s">
         <v>39</v>
@@ -6704,7 +6704,7 @@
         <v>86</v>
       </c>
       <c r="CE23" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="CG23" t="s">
         <v>232</v>
@@ -6716,7 +6716,7 @@
         <v>69</v>
       </c>
       <c r="CK23" s="14" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
     </row>
     <row r="24" spans="1:89" ht="17">
@@ -6825,7 +6825,7 @@
       </c>
       <c r="AV24" s="1"/>
       <c r="AW24" s="1" t="s">
-        <v>409</v>
+        <v>569</v>
       </c>
       <c r="AX24" s="1" t="s">
         <v>37</v>
@@ -6839,7 +6839,7 @@
       </c>
       <c r="BB24" s="1"/>
       <c r="BC24" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="BD24" s="10" t="s">
         <v>71</v>
@@ -6878,7 +6878,7 @@
         <v>71</v>
       </c>
       <c r="BU24" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="BV24" t="s">
         <v>57</v>
@@ -6893,25 +6893,25 @@
         <v>262</v>
       </c>
       <c r="CB24" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="CD24" t="s">
         <v>64</v>
       </c>
       <c r="CE24" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="CG24" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="CH24" s="14" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="CJ24" s="14" t="s">
         <v>142</v>
       </c>
       <c r="CK24" s="14" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
     </row>
     <row r="25" spans="1:89" ht="17">
@@ -6929,7 +6929,7 @@
         <v>187</v>
       </c>
       <c r="H25" s="7" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="I25" s="1"/>
       <c r="J25" s="1" t="s">
@@ -6992,7 +6992,7 @@
       </c>
       <c r="AJ25" s="1"/>
       <c r="AK25" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="AL25" s="1" t="s">
         <v>71</v>
@@ -7076,10 +7076,10 @@
         <v>176</v>
       </c>
       <c r="BV25" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="BX25" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="BY25" t="s">
         <v>57</v>
@@ -7088,7 +7088,7 @@
         <v>282</v>
       </c>
       <c r="CB25" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="CD25" t="s">
         <v>253</v>
@@ -7100,7 +7100,7 @@
         <v>98</v>
       </c>
       <c r="CH25" s="14" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="CJ25" s="14" t="s">
         <v>156</v>
@@ -7124,7 +7124,7 @@
         <v>58</v>
       </c>
       <c r="H26" s="7" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="I26" s="1"/>
       <c r="J26" s="1" t="s">
@@ -7272,10 +7272,10 @@
         <v>39</v>
       </c>
       <c r="BU26" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="BV26" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="BX26" t="s">
         <v>199</v>
@@ -7305,7 +7305,7 @@
         <v>168</v>
       </c>
       <c r="CK26" s="14" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="27" spans="1:89" ht="17">
@@ -7317,7 +7317,7 @@
       </c>
       <c r="C27" s="1"/>
       <c r="D27" s="7" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="E27" s="7" t="s">
         <v>37</v>
@@ -7478,7 +7478,7 @@
         <v>42</v>
       </c>
       <c r="BV27" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="BX27" t="s">
         <v>295</v>
@@ -7496,19 +7496,19 @@
         <v>89</v>
       </c>
       <c r="CE27" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="CG27" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="CH27" s="14" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="CJ27" s="14" t="s">
         <v>55</v>
       </c>
       <c r="CK27" s="14" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="28" spans="1:89" ht="17">
@@ -7666,7 +7666,7 @@
         <v>41</v>
       </c>
       <c r="BO28" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="BP28" t="s">
         <v>41</v>
@@ -7690,7 +7690,7 @@
         <v>159</v>
       </c>
       <c r="CA28" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="CB28" t="s">
         <v>39</v>
@@ -7699,19 +7699,19 @@
         <v>59</v>
       </c>
       <c r="CE28" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="CG28" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="CH28" s="14" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="CJ28" s="14" t="s">
         <v>55</v>
       </c>
       <c r="CK28" s="14" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
     </row>
     <row r="29" spans="1:89" ht="17">
@@ -7863,13 +7863,13 @@
       </c>
       <c r="BK29" s="1"/>
       <c r="BL29" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="BM29" s="7" t="s">
         <v>72</v>
       </c>
       <c r="BO29" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="BP29" t="s">
         <v>53</v>
@@ -7896,7 +7896,7 @@
         <v>317</v>
       </c>
       <c r="CB29" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="CD29" t="s">
         <v>256</v>
@@ -7914,12 +7914,12 @@
         <v>158</v>
       </c>
       <c r="CK29" s="14" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="30" spans="1:89" ht="17">
       <c r="A30" s="7" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="B30" s="7" t="s">
         <v>35</v>
@@ -7929,14 +7929,14 @@
         <v>210</v>
       </c>
       <c r="E30" s="7" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="F30" s="1"/>
       <c r="G30" s="8" t="s">
+        <v>439</v>
+      </c>
+      <c r="H30" s="7" t="s">
         <v>440</v>
-      </c>
-      <c r="H30" s="7" t="s">
-        <v>441</v>
       </c>
       <c r="I30" s="1"/>
       <c r="J30" s="1" t="s">
@@ -8052,7 +8052,7 @@
       </c>
       <c r="BE30" s="1"/>
       <c r="BF30" s="1" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="BG30" s="7" t="s">
         <v>37</v>
@@ -8062,7 +8062,7 @@
         <v>307</v>
       </c>
       <c r="BJ30" s="1" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="BK30" s="1"/>
       <c r="BL30" t="s">
@@ -8090,10 +8090,10 @@
         <v>259</v>
       </c>
       <c r="BX30" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="BY30" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="CA30" t="s">
         <v>307</v>
@@ -8111,7 +8111,7 @@
         <v>162</v>
       </c>
       <c r="CH30" s="14" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="CJ30" s="14" t="s">
         <v>158</v>
@@ -8262,17 +8262,17 @@
       </c>
       <c r="BH31" s="1"/>
       <c r="BI31" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="BJ31" t="s">
         <v>41</v>
       </c>
       <c r="BK31" s="1"/>
       <c r="BL31" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="BM31" s="7" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="BO31" t="s">
         <v>396</v>
@@ -8287,7 +8287,7 @@
         <v>39</v>
       </c>
       <c r="BU31" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="BV31" t="s">
         <v>39</v>
@@ -8296,10 +8296,10 @@
         <v>341</v>
       </c>
       <c r="BY31" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="CA31" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="CB31" t="s">
         <v>41</v>
@@ -8308,7 +8308,7 @@
         <v>189</v>
       </c>
       <c r="CE31" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="CG31" t="s">
         <v>162</v>
@@ -8320,7 +8320,7 @@
         <v>312</v>
       </c>
       <c r="CK31" s="14" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
     </row>
     <row r="32" spans="1:89" ht="17">
@@ -8435,21 +8435,21 @@
       </c>
       <c r="BB32" s="1"/>
       <c r="BC32" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="BD32" s="7" t="s">
         <v>57</v>
       </c>
       <c r="BE32" s="1"/>
       <c r="BF32" s="1" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="BG32" s="7" t="s">
         <v>37</v>
       </c>
       <c r="BH32" s="1"/>
       <c r="BI32" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="BJ32" s="7" t="s">
         <v>37</v>
@@ -8462,7 +8462,7 @@
         <v>37</v>
       </c>
       <c r="BO32" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="BP32" s="7" t="s">
         <v>71</v>
@@ -8477,13 +8477,13 @@
         <v>49</v>
       </c>
       <c r="BV32" t="s">
+        <v>540</v>
+      </c>
+      <c r="BX32" t="s">
+        <v>506</v>
+      </c>
+      <c r="BY32" t="s">
         <v>541</v>
-      </c>
-      <c r="BX32" t="s">
-        <v>507</v>
-      </c>
-      <c r="BY32" t="s">
-        <v>542</v>
       </c>
       <c r="CA32" t="s">
         <v>58</v>
@@ -8492,19 +8492,19 @@
         <v>33</v>
       </c>
       <c r="CD32" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="CE32" t="s">
         <v>39</v>
       </c>
       <c r="CG32" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="CH32" s="14" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="CJ32" s="14" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="CK32" s="14" t="s">
         <v>39</v>
@@ -8512,7 +8512,7 @@
     </row>
     <row r="33" spans="1:89" ht="17">
       <c r="A33" s="8" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="B33" s="7" t="s">
         <v>35</v>
@@ -8526,7 +8526,7 @@
       </c>
       <c r="F33" s="1"/>
       <c r="G33" s="7" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="H33" s="7" t="s">
         <v>41</v>
@@ -8625,7 +8625,7 @@
       </c>
       <c r="BE33" s="1"/>
       <c r="BF33" s="7" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="BG33" s="10" t="s">
         <v>71</v>
@@ -8651,7 +8651,7 @@
         <v>37</v>
       </c>
       <c r="BR33" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="BS33" t="s">
         <v>33</v>
@@ -8660,37 +8660,37 @@
         <v>334</v>
       </c>
       <c r="BV33" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="BX33" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="BY33" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="CA33" t="s">
         <v>404</v>
       </c>
       <c r="CB33" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="CD33" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="CE33" t="s">
+        <v>540</v>
+      </c>
+      <c r="CG33" t="s">
+        <v>567</v>
+      </c>
+      <c r="CH33" s="14" t="s">
+        <v>540</v>
+      </c>
+      <c r="CJ33" s="14" t="s">
+        <v>520</v>
+      </c>
+      <c r="CK33" s="14" t="s">
         <v>541</v>
-      </c>
-      <c r="CG33" t="s">
-        <v>568</v>
-      </c>
-      <c r="CH33" s="14" t="s">
-        <v>541</v>
-      </c>
-      <c r="CJ33" s="14" t="s">
-        <v>521</v>
-      </c>
-      <c r="CK33" s="14" t="s">
-        <v>542</v>
       </c>
     </row>
     <row r="34" spans="1:89" ht="17">
@@ -8702,14 +8702,14 @@
       </c>
       <c r="C34" s="1"/>
       <c r="D34" s="7" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="E34" s="7" t="s">
         <v>37</v>
       </c>
       <c r="F34" s="1"/>
       <c r="G34" s="7" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="H34" s="7" t="s">
         <v>259</v>
@@ -8830,7 +8830,7 @@
       </c>
       <c r="BK34" s="1"/>
       <c r="BL34" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="BM34" s="7" t="s">
         <v>83</v>
@@ -8851,13 +8851,13 @@
         <v>80</v>
       </c>
       <c r="BV34" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="BX34" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="BY34" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="CA34" t="s">
         <v>307</v>
@@ -8866,10 +8866,10 @@
         <v>57</v>
       </c>
       <c r="CD34" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="CE34" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="CG34" t="s">
         <v>335</v>
@@ -8899,7 +8899,7 @@
         <v>21</v>
       </c>
       <c r="H35" s="7" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="I35" s="1"/>
       <c r="J35" s="1" t="s">
@@ -9042,22 +9042,22 @@
         <v>49</v>
       </c>
       <c r="BV35" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="BX35" t="s">
         <v>362</v>
       </c>
       <c r="BY35" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="CA35" t="s">
         <v>262</v>
       </c>
       <c r="CB35" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="CD35" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="CE35" t="s">
         <v>39</v>
@@ -9086,7 +9086,7 @@
         <v>175</v>
       </c>
       <c r="H36" s="7" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="I36" s="1"/>
       <c r="J36" s="1" t="s">
@@ -9189,7 +9189,7 @@
       </c>
       <c r="BH36" s="1"/>
       <c r="BI36" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="BJ36" s="7" t="s">
         <v>83</v>
@@ -9217,22 +9217,22 @@
         <v>111</v>
       </c>
       <c r="BV36" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="BX36" t="s">
         <v>70</v>
       </c>
       <c r="BY36" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="CA36" t="s">
         <v>149</v>
       </c>
       <c r="CB36" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="CD36" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="CE36" t="s">
         <v>57</v>
@@ -9241,7 +9241,7 @@
         <v>301</v>
       </c>
       <c r="CH36" s="14" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="CJ36" s="14" t="s">
         <v>307</v>
@@ -9255,14 +9255,14 @@
         <v>67</v>
       </c>
       <c r="B37" s="7" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="C37" s="1"/>
       <c r="D37" s="7" t="s">
         <v>268</v>
       </c>
       <c r="E37" s="7" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="F37" s="1"/>
       <c r="G37" s="7" t="s">
@@ -9408,13 +9408,13 @@
         <v>329</v>
       </c>
       <c r="BV37" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="BX37" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="BY37" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="CA37" t="s">
         <v>84</v>
@@ -9426,19 +9426,19 @@
         <v>292</v>
       </c>
       <c r="CE37" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="CG37" t="s">
         <v>341</v>
       </c>
       <c r="CH37" s="14" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="CJ37" s="14" t="s">
         <v>305</v>
       </c>
       <c r="CK37" s="14" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="38" spans="1:89" ht="20">
@@ -9449,14 +9449,14 @@
         <v>148</v>
       </c>
       <c r="E38" s="7" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="F38" s="1"/>
       <c r="G38" s="7" t="s">
         <v>59</v>
       </c>
       <c r="H38" s="7" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="I38" s="1"/>
       <c r="J38" s="1" t="s">
@@ -9542,7 +9542,7 @@
       </c>
       <c r="AY38" s="1"/>
       <c r="AZ38" s="1" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="BA38" s="1" t="s">
         <v>266</v>
@@ -9570,13 +9570,13 @@
       </c>
       <c r="BK38" s="1"/>
       <c r="BL38" s="13" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="BM38" t="s">
         <v>266</v>
       </c>
       <c r="BO38" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="BP38" t="s">
         <v>61</v>
@@ -9591,13 +9591,13 @@
         <v>52</v>
       </c>
       <c r="BV38" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="BX38" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="BY38" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="CA38" t="s">
         <v>140</v>
@@ -9609,19 +9609,19 @@
         <v>334</v>
       </c>
       <c r="CE38" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="CG38" t="s">
         <v>341</v>
       </c>
       <c r="CH38" s="14" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="CJ38" s="14" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="CK38" s="14" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
     </row>
     <row r="39" spans="1:89" ht="17">
@@ -9632,7 +9632,7 @@
         <v>140</v>
       </c>
       <c r="E39" s="7" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="F39" s="1"/>
       <c r="G39" s="7" t="s">
@@ -9746,7 +9746,7 @@
       </c>
       <c r="BH39" s="1"/>
       <c r="BI39" s="7" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="BJ39" s="10" t="s">
         <v>71</v>
@@ -9780,7 +9780,7 @@
         <v>228</v>
       </c>
       <c r="BY39" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="CA39" t="s">
         <v>58</v>
@@ -9792,7 +9792,7 @@
         <v>77</v>
       </c>
       <c r="CE39" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="CG39" t="s">
         <v>295</v>
@@ -9804,7 +9804,7 @@
         <v>140</v>
       </c>
       <c r="CK39" s="14" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
     </row>
     <row r="40" spans="1:89" ht="17">
@@ -9815,7 +9815,7 @@
         <v>48</v>
       </c>
       <c r="E40" s="7" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="F40" s="1"/>
       <c r="G40" s="1"/>
@@ -9922,10 +9922,10 @@
         <v>392</v>
       </c>
       <c r="BM40" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="BO40" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="BP40" t="s">
         <v>266</v>
@@ -9946,10 +9946,10 @@
         <v>362</v>
       </c>
       <c r="BY40" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="CA40" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="CB40" t="s">
         <v>61</v>
@@ -9958,19 +9958,19 @@
         <v>77</v>
       </c>
       <c r="CE40" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="CG40" t="s">
         <v>141</v>
       </c>
       <c r="CH40" s="14" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="CJ40" s="14" t="s">
         <v>354</v>
       </c>
       <c r="CK40" s="14" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="41" spans="1:89" ht="17">
@@ -9999,7 +9999,7 @@
       </c>
       <c r="L41" s="1"/>
       <c r="M41" s="4" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="N41" s="4" t="s">
         <v>366</v>
@@ -10083,7 +10083,7 @@
         <v>129</v>
       </c>
       <c r="BG41" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="BH41" s="1"/>
       <c r="BI41" s="7" t="s">
@@ -10103,7 +10103,7 @@
         <v>145</v>
       </c>
       <c r="BP41" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="BR41" t="s">
         <v>220</v>
@@ -10121,31 +10121,31 @@
         <v>341</v>
       </c>
       <c r="BY41" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="CA41" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="CB41" t="s">
         <v>266</v>
       </c>
       <c r="CD41" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="CE41" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="CG41" t="s">
         <v>228</v>
       </c>
       <c r="CH41" s="14" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="CJ41" s="14" t="s">
         <v>354</v>
       </c>
       <c r="CK41" s="14" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
     </row>
     <row r="42" spans="1:89" ht="17">
@@ -10156,7 +10156,7 @@
         <v>82</v>
       </c>
       <c r="E42" s="7" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="F42" s="1"/>
       <c r="G42" s="7" t="s">
@@ -10244,7 +10244,7 @@
       </c>
       <c r="BB42" s="1"/>
       <c r="BC42" s="1" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="BD42" t="s">
         <v>61</v>
@@ -10265,13 +10265,13 @@
       </c>
       <c r="BK42" s="1"/>
       <c r="BO42" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="BP42" t="s">
         <v>393</v>
       </c>
       <c r="BR42" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="BS42" t="s">
         <v>61</v>
@@ -10280,7 +10280,7 @@
         <v>67</v>
       </c>
       <c r="BV42" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="BX42" t="s">
         <v>141</v>
@@ -10289,22 +10289,22 @@
         <v>41</v>
       </c>
       <c r="CA42" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="CB42" t="s">
         <v>266</v>
       </c>
       <c r="CD42" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="CE42" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="CG42" t="s">
         <v>268</v>
       </c>
       <c r="CH42" s="14" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="CJ42" s="14" t="s">
         <v>151</v>
@@ -10318,7 +10318,7 @@
       <c r="B43" s="1"/>
       <c r="C43" s="1"/>
       <c r="D43" s="8" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="E43" s="7" t="s">
         <v>37</v>
@@ -10405,7 +10405,7 @@
       </c>
       <c r="BB43" s="1"/>
       <c r="BC43" s="1" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="BD43" t="s">
         <v>266</v>
@@ -10422,7 +10422,7 @@
       </c>
       <c r="BK43" s="1"/>
       <c r="BR43" s="7" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="BS43" t="s">
         <v>266</v>
@@ -10443,7 +10443,7 @@
         <v>338</v>
       </c>
       <c r="CB43" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="CD43" t="s">
         <v>108</v>
@@ -10458,7 +10458,7 @@
         <v>33</v>
       </c>
       <c r="CJ43" s="14" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="CK43" s="14" t="s">
         <v>41</v>
@@ -10472,7 +10472,7 @@
         <v>29</v>
       </c>
       <c r="E44" s="7" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="F44" s="1"/>
       <c r="G44" s="7" t="s">
@@ -10503,7 +10503,7 @@
       <c r="T44" s="1"/>
       <c r="U44" s="1"/>
       <c r="V44" s="1" t="s">
-        <v>409</v>
+        <v>569</v>
       </c>
       <c r="W44" s="1" t="s">
         <v>35</v>
@@ -10577,7 +10577,7 @@
         <v>33</v>
       </c>
       <c r="BX44" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="BY44" t="s">
         <v>61</v>
@@ -10598,10 +10598,10 @@
         <v>28</v>
       </c>
       <c r="CH44" s="14" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="CJ44" s="14" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="CK44" s="14" t="s">
         <v>83</v>
@@ -10690,14 +10690,14 @@
         <v>114</v>
       </c>
       <c r="BD45" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="BE45" s="1"/>
       <c r="BF45" s="1"/>
       <c r="BG45" s="1"/>
       <c r="BH45" s="1"/>
       <c r="BI45" s="7" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="BJ45" t="s">
         <v>266</v>
@@ -10707,37 +10707,37 @@
         <v>303</v>
       </c>
       <c r="BS45" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="BU45" t="s">
         <v>80</v>
       </c>
       <c r="BV45" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="BX45" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="BY45" t="s">
         <v>266</v>
       </c>
       <c r="CD45" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="CE45" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="CG45" t="s">
         <v>329</v>
       </c>
       <c r="CH45" s="14" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="CJ45" s="14" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="CK45" s="14" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
     </row>
     <row r="46" spans="1:89" ht="17">
@@ -10820,7 +10820,7 @@
       <c r="BA46" s="1"/>
       <c r="BB46" s="1"/>
       <c r="BC46" s="1" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="BD46" t="s">
         <v>393</v>
@@ -10843,7 +10843,7 @@
         <v>393</v>
       </c>
       <c r="BU46" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="BV46" t="s">
         <v>61</v>
@@ -10858,10 +10858,10 @@
         <v>329</v>
       </c>
       <c r="CH46" s="14" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="CJ46" s="14" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="CK46" s="14" t="s">
         <v>57</v>
@@ -10878,7 +10878,7 @@
         <v>55</v>
       </c>
       <c r="H47" s="7" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="I47" s="1"/>
       <c r="J47" s="1" t="s">
@@ -10952,29 +10952,29 @@
         <v>96</v>
       </c>
       <c r="BJ47" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="BK47" s="1"/>
       <c r="BU47" s="1" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="BV47" t="s">
         <v>266</v>
       </c>
       <c r="BX47" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="BY47" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="CG47" t="s">
         <v>340</v>
       </c>
       <c r="CH47" s="14" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="CJ47" s="14" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="CK47" s="14" t="s">
         <v>39</v>
@@ -10991,7 +10991,7 @@
         <v>42</v>
       </c>
       <c r="H48" s="7" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="I48" s="1"/>
       <c r="J48" s="1" t="s">
@@ -11073,7 +11073,7 @@
       </c>
       <c r="BK48" s="1"/>
       <c r="BU48" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="BV48" t="s">
         <v>266</v>
@@ -11088,7 +11088,7 @@
         <v>215</v>
       </c>
       <c r="CK48" s="14" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
     </row>
     <row r="49" spans="1:74">
@@ -11179,7 +11179,7 @@
         <v>91</v>
       </c>
       <c r="BV49" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
     </row>
     <row r="50" spans="1:74">
@@ -11259,7 +11259,7 @@
       <c r="BJ50" s="1"/>
       <c r="BK50" s="1"/>
       <c r="BU50" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="BV50" t="s">
         <v>393</v>
@@ -11387,7 +11387,7 @@
       <c r="Z52" s="1"/>
       <c r="AA52" s="1"/>
       <c r="AB52" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="AC52" s="1" t="s">
         <v>398</v>
@@ -11667,7 +11667,7 @@
         <v>32</v>
       </c>
       <c r="H56" s="7" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="I56" s="1"/>
       <c r="J56" s="1"/>
@@ -11821,7 +11821,7 @@
         <v>46</v>
       </c>
       <c r="H58" s="7" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="I58" s="1"/>
       <c r="J58" s="1"/>
@@ -11898,7 +11898,7 @@
         <v>26</v>
       </c>
       <c r="H59" s="7" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="I59" s="1"/>
       <c r="J59" s="1"/>
@@ -73168,100 +73168,100 @@
         <v>70</v>
       </c>
       <c r="B1" t="s">
+        <v>522</v>
+      </c>
+      <c r="C1" t="s">
+        <v>470</v>
+      </c>
+      <c r="D1" t="s">
+        <v>497</v>
+      </c>
+      <c r="E1" t="s">
+        <v>462</v>
+      </c>
+      <c r="F1" t="s">
+        <v>498</v>
+      </c>
+      <c r="G1" t="s">
         <v>523</v>
       </c>
-      <c r="C1" t="s">
+      <c r="H1" t="s">
+        <v>524</v>
+      </c>
+      <c r="I1" t="s">
+        <v>485</v>
+      </c>
+      <c r="J1" t="s">
         <v>471</v>
       </c>
-      <c r="D1" t="s">
-        <v>498</v>
-      </c>
-      <c r="E1" t="s">
+      <c r="K1" t="s">
+        <v>499</v>
+      </c>
+      <c r="L1" t="s">
+        <v>472</v>
+      </c>
+      <c r="M1" t="s">
+        <v>500</v>
+      </c>
+      <c r="N1" t="s">
+        <v>525</v>
+      </c>
+      <c r="O1" t="s">
+        <v>501</v>
+      </c>
+      <c r="P1" t="s">
+        <v>473</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>474</v>
+      </c>
+      <c r="R1" t="s">
+        <v>502</v>
+      </c>
+      <c r="S1" t="s">
+        <v>526</v>
+      </c>
+      <c r="T1" t="s">
+        <v>527</v>
+      </c>
+      <c r="U1" t="s">
+        <v>475</v>
+      </c>
+      <c r="V1" t="s">
+        <v>528</v>
+      </c>
+      <c r="W1" t="s">
+        <v>529</v>
+      </c>
+      <c r="X1" t="s">
+        <v>530</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>476</v>
+      </c>
+      <c r="Z1" t="s">
         <v>463</v>
       </c>
-      <c r="F1" t="s">
-        <v>499</v>
-      </c>
-      <c r="G1" t="s">
-        <v>524</v>
-      </c>
-      <c r="H1" t="s">
-        <v>525</v>
-      </c>
-      <c r="I1" t="s">
-        <v>486</v>
-      </c>
-      <c r="J1" t="s">
-        <v>472</v>
-      </c>
-      <c r="K1" t="s">
-        <v>500</v>
-      </c>
-      <c r="L1" t="s">
-        <v>473</v>
-      </c>
-      <c r="M1" t="s">
-        <v>501</v>
-      </c>
-      <c r="N1" t="s">
-        <v>526</v>
-      </c>
-      <c r="O1" t="s">
-        <v>502</v>
-      </c>
-      <c r="P1" t="s">
-        <v>474</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>475</v>
-      </c>
-      <c r="R1" t="s">
+      <c r="AA1" t="s">
         <v>503</v>
       </c>
-      <c r="S1" t="s">
-        <v>527</v>
-      </c>
-      <c r="T1" t="s">
-        <v>528</v>
-      </c>
-      <c r="U1" t="s">
-        <v>476</v>
-      </c>
-      <c r="V1" t="s">
-        <v>529</v>
-      </c>
-      <c r="W1" t="s">
-        <v>530</v>
-      </c>
-      <c r="X1" t="s">
+      <c r="AB1" t="s">
         <v>531</v>
       </c>
-      <c r="Y1" t="s">
+      <c r="AC1" t="s">
         <v>477</v>
       </c>
-      <c r="Z1" t="s">
-        <v>464</v>
-      </c>
-      <c r="AA1" t="s">
+      <c r="AD1" t="s">
         <v>504</v>
       </c>
-      <c r="AB1" t="s">
+      <c r="AE1" t="s">
         <v>532</v>
       </c>
-      <c r="AC1" t="s">
+      <c r="AF1" t="s">
+        <v>533</v>
+      </c>
+      <c r="AG1" t="s">
         <v>478</v>
-      </c>
-      <c r="AD1" t="s">
-        <v>505</v>
-      </c>
-      <c r="AE1" t="s">
-        <v>533</v>
-      </c>
-      <c r="AF1" t="s">
-        <v>534</v>
-      </c>
-      <c r="AG1" t="s">
-        <v>479</v>
       </c>
     </row>
     <row r="3" spans="1:33" ht="25">
@@ -73275,7 +73275,7 @@
     </row>
     <row r="4" spans="1:33">
       <c r="A4" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="B4" t="str">
         <f t="shared" ref="B4:B38" si="0">TRIM(A4)</f>
@@ -73284,7 +73284,7 @@
     </row>
     <row r="5" spans="1:33">
       <c r="A5" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="B5" t="str">
         <f t="shared" si="0"/>
@@ -73293,7 +73293,7 @@
     </row>
     <row r="6" spans="1:33">
       <c r="A6" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="B6" t="str">
         <f t="shared" si="0"/>
@@ -73302,7 +73302,7 @@
     </row>
     <row r="7" spans="1:33">
       <c r="A7" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="B7" t="str">
         <f t="shared" si="0"/>
@@ -73311,7 +73311,7 @@
     </row>
     <row r="8" spans="1:33">
       <c r="A8" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="B8" t="str">
         <f t="shared" si="0"/>
@@ -73320,7 +73320,7 @@
     </row>
     <row r="9" spans="1:33">
       <c r="A9" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="B9" t="str">
         <f t="shared" si="0"/>
@@ -73329,7 +73329,7 @@
     </row>
     <row r="10" spans="1:33">
       <c r="A10" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="B10" t="str">
         <f t="shared" si="0"/>
@@ -73338,7 +73338,7 @@
     </row>
     <row r="11" spans="1:33">
       <c r="A11" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="B11" t="str">
         <f t="shared" si="0"/>
@@ -73347,7 +73347,7 @@
     </row>
     <row r="12" spans="1:33">
       <c r="A12" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="B12" t="str">
         <f t="shared" si="0"/>
@@ -73356,7 +73356,7 @@
     </row>
     <row r="13" spans="1:33">
       <c r="A13" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="B13" t="str">
         <f t="shared" si="0"/>
@@ -73365,7 +73365,7 @@
     </row>
     <row r="14" spans="1:33">
       <c r="A14" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="B14" t="str">
         <f t="shared" si="0"/>
@@ -73374,7 +73374,7 @@
     </row>
     <row r="15" spans="1:33">
       <c r="A15" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="B15" t="str">
         <f t="shared" si="0"/>
@@ -73383,7 +73383,7 @@
     </row>
     <row r="16" spans="1:33">
       <c r="A16" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="B16" t="str">
         <f t="shared" si="0"/>
@@ -73392,7 +73392,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="B17" t="str">
         <f t="shared" si="0"/>
@@ -73401,7 +73401,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="B18" t="str">
         <f t="shared" si="0"/>
@@ -73410,7 +73410,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="B19" t="str">
         <f t="shared" si="0"/>
@@ -73419,7 +73419,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="B20" t="str">
         <f t="shared" si="0"/>
@@ -73428,7 +73428,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="B21" t="str">
         <f t="shared" si="0"/>
@@ -73437,7 +73437,7 @@
     </row>
     <row r="22" spans="1:2">
       <c r="A22" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="B22" t="str">
         <f t="shared" si="0"/>
@@ -73446,7 +73446,7 @@
     </row>
     <row r="23" spans="1:2">
       <c r="A23" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="B23" t="str">
         <f t="shared" si="0"/>
@@ -73455,7 +73455,7 @@
     </row>
     <row r="24" spans="1:2">
       <c r="A24" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="B24" t="str">
         <f t="shared" si="0"/>
@@ -73464,7 +73464,7 @@
     </row>
     <row r="25" spans="1:2">
       <c r="A25" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="B25" t="str">
         <f t="shared" si="0"/>
@@ -73473,7 +73473,7 @@
     </row>
     <row r="26" spans="1:2">
       <c r="A26" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="B26" t="str">
         <f t="shared" si="0"/>
@@ -73482,7 +73482,7 @@
     </row>
     <row r="27" spans="1:2">
       <c r="A27" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="B27" t="str">
         <f t="shared" si="0"/>
@@ -73491,7 +73491,7 @@
     </row>
     <row r="28" spans="1:2">
       <c r="A28" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="B28" t="str">
         <f t="shared" si="0"/>
@@ -73500,7 +73500,7 @@
     </row>
     <row r="29" spans="1:2">
       <c r="A29" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="B29" t="str">
         <f t="shared" si="0"/>
@@ -73509,7 +73509,7 @@
     </row>
     <row r="30" spans="1:2">
       <c r="A30" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="B30" t="str">
         <f t="shared" si="0"/>
@@ -73518,7 +73518,7 @@
     </row>
     <row r="31" spans="1:2">
       <c r="A31" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="B31" t="str">
         <f t="shared" si="0"/>
@@ -73527,7 +73527,7 @@
     </row>
     <row r="32" spans="1:2">
       <c r="A32" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="B32" t="str">
         <f t="shared" si="0"/>
@@ -73536,7 +73536,7 @@
     </row>
     <row r="33" spans="1:2">
       <c r="A33" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="B33" t="str">
         <f t="shared" si="0"/>
@@ -73545,7 +73545,7 @@
     </row>
     <row r="34" spans="1:2">
       <c r="A34" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="B34" t="str">
         <f t="shared" si="0"/>
@@ -73554,7 +73554,7 @@
     </row>
     <row r="35" spans="1:2">
       <c r="A35" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="B35" t="str">
         <f t="shared" si="0"/>
